--- a/artfynd/A 54093-2024 artfynd.xlsx
+++ b/artfynd/A 54093-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103049153</v>
+        <v>103049147</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600264.2631896475</v>
+        <v>600265</v>
       </c>
       <c r="R2" t="n">
-        <v>7078124.635997791</v>
+        <v>7078125</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>103049159</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -834,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600165.776050714</v>
+        <v>600166</v>
       </c>
       <c r="R3" t="n">
-        <v>7078090.556399241</v>
+        <v>7078090</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +847,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103049161</v>
+        <v>103049153</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -950,13 +915,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600118.0812915446</v>
+        <v>600264</v>
       </c>
       <c r="R4" t="n">
-        <v>7078045.722426034</v>
+        <v>7078125</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,19 +948,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103049147</v>
+        <v>103049161</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,13 +1016,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600265.1473894047</v>
+        <v>600118</v>
       </c>
       <c r="R5" t="n">
-        <v>7078124.664216249</v>
+        <v>7078046</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,19 +1049,9 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 54093-2024 artfynd.xlsx
+++ b/artfynd/A 54093-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103049147</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103049159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103049153</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103049161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>